--- a/MPR_Managerment/Templates/pnk_template_v2.xlsx
+++ b/MPR_Managerment/Templates/pnk_template_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUAN DAT\OneDrive\Working\Final_Project_DLHI_Management\MPR_Managerment\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c02630c4a1efac79/Working/Final_Project_DLHI_Management/MPR_Managerment/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A73C2E-4554-40D0-B17C-78437B84C1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F6A73C2E-4554-40D0-B17C-78437B84C1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C3AB64B-DF63-4E04-9FC6-0D4876EE1F7A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EBD75BFF-117A-4792-9F82-FA7699CF60C2}"/>
   </bookViews>
@@ -184,10 +184,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -518,7 +518,7 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -534,18 +534,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -557,7 +557,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -569,16 +569,16 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -587,7 +587,7 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -605,7 +605,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -630,18 +630,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -657,7 +657,7 @@
     <xf numFmtId="4" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -666,18 +666,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -687,9 +687,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -702,14 +702,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -719,7 +719,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -747,6 +747,21 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -791,21 +806,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1190,6 +1190,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1CFD77-4A96-4221-8AD7-6639E3518607}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:IS29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
@@ -1924,17 +1927,17 @@
       <c r="E5" s="55"/>
     </row>
     <row r="6" spans="1:253" ht="69" customHeight="1">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
     </row>
     <row r="7" spans="1:253" s="76" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
       <c r="A7" s="77"/>
@@ -1959,15 +1962,15 @@
         <v>37</v>
       </c>
       <c r="D8" s="74"/>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="92"/>
-      <c r="G8" s="95" t="s">
+      <c r="F8" s="97"/>
+      <c r="G8" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="99" t="s">
+      <c r="H8" s="101"/>
+      <c r="I8" s="104" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1980,11 +1983,11 @@
         <v>32</v>
       </c>
       <c r="D9" s="70"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="100"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="105"/>
       <c r="J9" s="52"/>
       <c r="K9" s="52"/>
       <c r="L9" s="52"/>
@@ -3288,15 +3291,15 @@
       </c>
     </row>
     <row r="15" spans="1:253" s="48" customFormat="1" ht="39" customHeight="1">
-      <c r="A15" s="101"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
     </row>
     <row r="16" spans="1:253" s="43" customFormat="1" ht="52.5" customHeight="1">
       <c r="A16" s="47"/>
@@ -3327,14 +3330,14 @@
       <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:248" s="34" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="88"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="93"/>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
@@ -5905,7 +5908,7 @@
     <mergeCell ref="I8:I9"/>
   </mergeCells>
   <pageMargins left="0.24" right="0.16" top="0.32" bottom="0.28999999999999998" header="0.42" footer="0.3"/>
-  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>